--- a/royalty_result.xlsx
+++ b/royalty_result.xlsx
@@ -58,16 +58,16 @@
     <t>TS08UE5880</t>
   </si>
   <si>
-    <t>TMGA29782266</t>
-  </si>
-  <si>
-    <t>TMGA29782267</t>
-  </si>
-  <si>
-    <t>TMGA29782268</t>
-  </si>
-  <si>
-    <t>TMGA29782269</t>
+    <t>TMGA32019264</t>
+  </si>
+  <si>
+    <t>TMGA32019265</t>
+  </si>
+  <si>
+    <t>TMGA32019266</t>
+  </si>
+  <si>
+    <t>TMGA32019267</t>
   </si>
   <si>
     <t>9908076542</t>
@@ -115,7 +115,7 @@
     <t>5500</t>
   </si>
   <si>
-    <t>✅ Success</t>
+    <t>❌ Login Failed</t>
   </si>
 </sst>
 </file>
